--- a/excel/testdata/raw_header/2-row-simple/workbook.xlsx
+++ b/excel/testdata/raw_header/2-row-simple/workbook.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2-row-simple" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>

--- a/excel/testdata/raw_header/2-row-simple/workbook.xlsx
+++ b/excel/testdata/raw_header/2-row-simple/workbook.xlsx
@@ -46,15 +46,20 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -62,12 +67,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9E9E9E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9E9E9E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9E9E9E"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="true" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -339,26 +364,41 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
     </row>
   </sheetData>
 </worksheet>
